--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/03. Xác nhận bảo hành/XNBH_.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/03. Xác nhận bảo hành/XNBH_.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 05\03. Xác nhận bảo hành\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 09\03. Xác nhận bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A4396B-A1BB-45D5-8622-E07FAC5AC7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557D3685-32B6-4735-B030-8CF69826E070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$I$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$I$22</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -63,12 +63,6 @@
     <t>Địa chỉ:</t>
   </si>
   <si>
-    <t>ĐT: 0915 223 399</t>
-  </si>
-  <si>
-    <t>ĐC: AA46 TT19 KĐT Văn Quán, Phường Văn Quán, Quận Hà Đông, Hà Nội</t>
-  </si>
-  <si>
     <t xml:space="preserve">                                        </t>
   </si>
   <si>
@@ -112,6 +106,15 @@
   </si>
   <si>
     <t>Hướng Xử Lý</t>
+  </si>
+  <si>
+    <t>Địa chỉ: A46 TT19 KĐT Văn Quán, Phường Văn Quán, Quận Hà Đông, Hà Nội</t>
+  </si>
+  <si>
+    <t>Điện thoại: 0243 6400 767</t>
+  </si>
+  <si>
+    <t>Hà Nội, ngày  tháng  năm 2026</t>
   </si>
 </sst>
 </file>
@@ -121,7 +124,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@*."/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,12 +161,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -248,28 +245,26 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <b/>
-      <sz val="10"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
+      <i/>
+      <sz val="8"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -423,15 +418,9 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -448,85 +437,109 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -535,62 +548,38 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -614,16 +603,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>91505</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>98833</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>132521</xdr:rowOff>
+      <xdr:rowOff>147176</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>798635</xdr:colOff>
+      <xdr:colOff>381001</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>99391</xdr:rowOff>
+      <xdr:rowOff>65943</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -652,8 +641,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="91505" y="132521"/>
-          <a:ext cx="2069938" cy="640947"/>
+          <a:off x="472506" y="147176"/>
+          <a:ext cx="1271303" cy="497594"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -952,277 +941,280 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.140625" style="4" customWidth="1"/>
-    <col min="8" max="9" width="18.7109375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="24.140625" style="2" customWidth="1"/>
+    <col min="8" max="9" width="18.7109375" style="5" customWidth="1"/>
     <col min="10" max="12" width="9.140625" style="1"/>
     <col min="13" max="13" width="0" style="1" hidden="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="9" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46"/>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="37" t="s">
+    <row r="1" spans="1:13" s="7" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+    </row>
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+    </row>
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="40"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+    </row>
+    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-    </row>
-    <row r="2" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-    </row>
-    <row r="3" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-    </row>
-    <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
       <c r="M8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
       <c r="L9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" s="53" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-    </row>
-    <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-    </row>
-    <row r="13" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D15" s="10" t="s">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+    </row>
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="23"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="30"/>
+    </row>
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-    </row>
-    <row r="16" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="56"/>
-    </row>
-    <row r="17" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="59" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="58"/>
-    </row>
-    <row r="18" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-    </row>
-    <row r="19" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="32"/>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -1230,101 +1222,90 @@
       <c r="E19" s="18"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-    </row>
-    <row r="20" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
     </row>
-    <row r="21" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-    </row>
-    <row r="22" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="21"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="57" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-    </row>
-    <row r="24" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="21"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="55"/>
-      <c r="C25" s="55"/>
-    </row>
-    <row r="64" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+    </row>
+    <row r="63" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="D3:I3"/>
     <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="H22:I22"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.51181102362204722" top="1.4960629921259843" bottom="0.98425196850393704" header="0.43307086614173229" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
